--- a/Config/Datas/InstantEncounterDatas/InstantEncounter.xlsx
+++ b/Config/Datas/InstantEncounterDatas/InstantEncounter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\InstantEncounterDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725B16EC-C7E0-43C5-BE92-D32E8372C2DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C097992C-5C63-4D54-9ED4-2A939E573EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -68,6 +68,10 @@
   </si>
   <si>
     <t>砍价_接受,砍价_不接受</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bargain</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -448,8 +452,8 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B3">
-        <v>1</v>
+      <c r="B3" t="s">
+        <v>11</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>

--- a/Config/Datas/InstantEncounterDatas/InstantEncounter.xlsx
+++ b/Config/Datas/InstantEncounterDatas/InstantEncounter.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\InstantEncounterDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C097992C-5C63-4D54-9ED4-2A939E573EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C87263-1C7F-4E7B-A7D5-CFB05C74C8BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
